--- a/結果記録.xlsx
+++ b/結果記録.xlsx
@@ -610,11 +610,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>125.04</v>
+        <v>174.01</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>荒野スイミング</t>
+          <t>菰野スイミング</t>
         </is>
       </c>
     </row>
